--- a/data/monthly/【2026年3月】月次数値.xlsx
+++ b/data/monthly/【2026年3月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="143">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -317,31 +316,162 @@
   </si>
   <si>
     <t>桐歯科医院</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -349,36 +479,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -667,14 +797,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y74"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -777,10 +904,10 @@
         <v>2674</v>
       </c>
       <c r="I2">
-        <v>1.452506</v>
+        <v>1.4525060000000001</v>
       </c>
       <c r="J2">
-        <v>55.27472527</v>
+        <v>55.274725269999998</v>
       </c>
       <c r="K2">
         <v>320</v>
@@ -798,16 +925,16 @@
         <v>3884</v>
       </c>
       <c r="P2">
-        <v>1295.056643</v>
+        <v>1295.0566429999999</v>
       </c>
       <c r="Q2">
         <v>91</v>
       </c>
       <c r="S2">
-        <v>55.274725</v>
+        <v>55.274724999999997</v>
       </c>
       <c r="T2">
-        <v>2.342945</v>
+        <v>2.3429449999999998</v>
       </c>
       <c r="U2">
         <v>94</v>
@@ -822,10 +949,10 @@
         <v>51</v>
       </c>
       <c r="Y2">
-        <v>98.627451</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>98.627450999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -887,19 +1014,19 @@
         <v>101</v>
       </c>
       <c r="V3">
-        <v>3.529001</v>
+        <v>3.5290010000000001</v>
       </c>
       <c r="W3">
-        <v>50.019802</v>
+        <v>50.019801999999999</v>
       </c>
       <c r="X3">
         <v>84</v>
       </c>
       <c r="Y3">
-        <v>60.142857</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>60.142856999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -928,7 +1055,7 @@
         <v>1.389222</v>
       </c>
       <c r="J4">
-        <v>67.25675676</v>
+        <v>67.256756760000002</v>
       </c>
       <c r="K4">
         <v>160</v>
@@ -946,13 +1073,13 @@
         <v>3944</v>
       </c>
       <c r="P4">
-        <v>1261.916836</v>
+        <v>1261.9168360000001</v>
       </c>
       <c r="Q4">
         <v>74</v>
       </c>
       <c r="S4">
-        <v>67.256757</v>
+        <v>67.256756999999993</v>
       </c>
       <c r="T4">
         <v>1.876268</v>
@@ -961,7 +1088,7 @@
         <v>79</v>
       </c>
       <c r="V4">
-        <v>2.003043</v>
+        <v>2.0030429999999999</v>
       </c>
       <c r="W4">
         <v>63</v>
@@ -970,10 +1097,10 @@
         <v>59</v>
       </c>
       <c r="Y4">
-        <v>84.355932</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>84.355931999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -999,10 +1126,10 @@
         <v>2511</v>
       </c>
       <c r="I5">
-        <v>1.571087</v>
+        <v>1.5710869999999999</v>
       </c>
       <c r="J5">
-        <v>56.62921348</v>
+        <v>56.629213479999997</v>
       </c>
       <c r="K5">
         <v>160</v>
@@ -1029,13 +1156,13 @@
         <v>56.629213</v>
       </c>
       <c r="T5">
-        <v>2.25602</v>
+        <v>2.2560199999999999</v>
       </c>
       <c r="U5">
         <v>96</v>
       </c>
       <c r="V5">
-        <v>2.43346</v>
+        <v>2.4334600000000002</v>
       </c>
       <c r="W5">
         <v>52.5</v>
@@ -1047,7 +1174,7 @@
         <v>76.363636</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1094,22 +1221,22 @@
         <v>3790</v>
       </c>
       <c r="P6">
-        <v>1316.094987</v>
+        <v>1316.0949869999999</v>
       </c>
       <c r="Q6">
         <v>83</v>
       </c>
       <c r="S6">
-        <v>60.096386</v>
+        <v>60.096386000000003</v>
       </c>
       <c r="T6">
-        <v>2.189974</v>
+        <v>2.1899739999999999</v>
       </c>
       <c r="U6">
         <v>88</v>
       </c>
       <c r="V6">
-        <v>2.3219</v>
+        <v>2.3218999999999999</v>
       </c>
       <c r="W6">
         <v>56.681818</v>
@@ -1121,7 +1248,7 @@
         <v>74.447761</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1150,7 +1277,7 @@
         <v>1.386968</v>
       </c>
       <c r="J7">
-        <v>33.43333333</v>
+        <v>33.433333330000004</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -1174,28 +1301,28 @@
         <v>150</v>
       </c>
       <c r="S7">
-        <v>33.433333</v>
+        <v>33.433332999999998</v>
       </c>
       <c r="T7">
-        <v>3.308337</v>
+        <v>3.3083369999999999</v>
       </c>
       <c r="U7">
         <v>168</v>
       </c>
       <c r="V7">
-        <v>3.705337</v>
+        <v>3.7053370000000001</v>
       </c>
       <c r="W7">
-        <v>29.85119</v>
+        <v>29.851189999999999</v>
       </c>
       <c r="X7">
         <v>120</v>
       </c>
       <c r="Y7">
-        <v>41.791667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>41.791666999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1221,10 +1348,10 @@
         <v>4120</v>
       </c>
       <c r="I8">
-        <v>1.323544</v>
+        <v>1.3235440000000001</v>
       </c>
       <c r="J8">
-        <v>37.77443609</v>
+        <v>37.774436090000002</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1242,34 +1369,34 @@
         <v>5453</v>
       </c>
       <c r="P8">
-        <v>921.32771</v>
+        <v>921.32771000000002</v>
       </c>
       <c r="Q8">
         <v>133</v>
       </c>
       <c r="S8">
-        <v>37.774436</v>
+        <v>37.774436000000001</v>
       </c>
       <c r="T8">
-        <v>2.439024</v>
+        <v>2.4390239999999999</v>
       </c>
       <c r="U8">
         <v>143</v>
       </c>
       <c r="V8">
-        <v>2.62241</v>
+        <v>2.6224099999999999</v>
       </c>
       <c r="W8">
-        <v>35.132867</v>
+        <v>35.132866999999997</v>
       </c>
       <c r="X8">
         <v>106</v>
       </c>
       <c r="Y8">
-        <v>47.396226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>47.396225999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1295,10 +1422,10 @@
         <v>5957</v>
       </c>
       <c r="I9">
-        <v>1.230485</v>
+        <v>1.2304850000000001</v>
       </c>
       <c r="J9">
-        <v>35.17682927</v>
+        <v>35.176829269999999</v>
       </c>
       <c r="K9" t="s">
         <v>42</v>
@@ -1316,22 +1443,22 @@
         <v>7330</v>
       </c>
       <c r="P9">
-        <v>787.039563</v>
+        <v>787.03956300000004</v>
       </c>
       <c r="Q9">
         <v>160</v>
       </c>
       <c r="S9">
-        <v>36.05625</v>
+        <v>36.056249999999999</v>
       </c>
       <c r="T9">
-        <v>2.18281</v>
+        <v>2.1828099999999999</v>
       </c>
       <c r="U9">
         <v>218</v>
       </c>
       <c r="V9">
-        <v>2.974079</v>
+        <v>2.9740790000000001</v>
       </c>
       <c r="W9">
         <v>26.463303</v>
@@ -1340,10 +1467,10 @@
         <v>164</v>
       </c>
       <c r="Y9">
-        <v>35.176829</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>35.176828999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1372,7 +1499,7 @@
         <v>1.553439</v>
       </c>
       <c r="J10">
-        <v>56.46363636</v>
+        <v>56.463636360000002</v>
       </c>
       <c r="K10" t="s">
         <v>42</v>
@@ -1399,25 +1526,25 @@
         <v>52.635593</v>
       </c>
       <c r="T10">
-        <v>3.529764</v>
+        <v>3.5297640000000001</v>
       </c>
       <c r="U10">
         <v>130</v>
       </c>
       <c r="V10">
-        <v>3.888723</v>
+        <v>3.8887230000000002</v>
       </c>
       <c r="W10">
-        <v>47.776923</v>
+        <v>47.776922999999996</v>
       </c>
       <c r="X10">
         <v>110</v>
       </c>
       <c r="Y10">
-        <v>56.463636</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>56.463636000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1443,10 +1570,10 @@
         <v>3299</v>
       </c>
       <c r="I11">
-        <v>1.612307</v>
+        <v>1.6123069999999999</v>
       </c>
       <c r="J11">
-        <v>58.20792079</v>
+        <v>58.207920790000003</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
@@ -1470,28 +1597,28 @@
         <v>110</v>
       </c>
       <c r="S11">
-        <v>53.445455</v>
+        <v>53.445455000000003</v>
       </c>
       <c r="T11">
-        <v>2.068058</v>
+        <v>2.0680580000000002</v>
       </c>
       <c r="U11">
         <v>118</v>
       </c>
       <c r="V11">
-        <v>2.218462</v>
+        <v>2.2184620000000002</v>
       </c>
       <c r="W11">
-        <v>49.822034</v>
+        <v>49.822034000000002</v>
       </c>
       <c r="X11">
         <v>101</v>
       </c>
       <c r="Y11">
-        <v>58.207921</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>58.207920999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1517,10 +1644,10 @@
         <v>3477</v>
       </c>
       <c r="I12">
-        <v>1.368421</v>
+        <v>1.3684210000000001</v>
       </c>
       <c r="J12">
-        <v>61.17171717</v>
+        <v>61.171717170000001</v>
       </c>
       <c r="K12" t="s">
         <v>42</v>
@@ -1538,13 +1665,13 @@
         <v>4758</v>
       </c>
       <c r="P12">
-        <v>1272.803699</v>
+        <v>1272.8036990000001</v>
       </c>
       <c r="Q12">
         <v>97</v>
       </c>
       <c r="S12">
-        <v>62.43299</v>
+        <v>62.432989999999997</v>
       </c>
       <c r="T12">
         <v>2.038672</v>
@@ -1553,19 +1680,19 @@
         <v>103</v>
       </c>
       <c r="V12">
-        <v>2.164775</v>
+        <v>2.1647750000000001</v>
       </c>
       <c r="W12">
-        <v>58.796117</v>
+        <v>58.796117000000002</v>
       </c>
       <c r="X12">
         <v>99</v>
       </c>
       <c r="Y12">
-        <v>61.171717</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>61.171717000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1594,7 +1721,7 @@
         <v>1.158237</v>
       </c>
       <c r="J13">
-        <v>65.81553398</v>
+        <v>65.815533979999998</v>
       </c>
       <c r="K13" t="s">
         <v>42</v>
@@ -1618,19 +1745,19 @@
         <v>82</v>
       </c>
       <c r="S13">
-        <v>82.670732</v>
+        <v>82.670732000000001</v>
       </c>
       <c r="T13">
-        <v>2.093973</v>
+        <v>2.0939730000000001</v>
       </c>
       <c r="U13">
         <v>99</v>
       </c>
       <c r="V13">
-        <v>2.52809</v>
+        <v>2.5280900000000002</v>
       </c>
       <c r="W13">
-        <v>68.474747</v>
+        <v>68.474746999999994</v>
       </c>
       <c r="X13">
         <v>103</v>
@@ -1639,7 +1766,7 @@
         <v>65.815534</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1665,10 +1792,10 @@
         <v>3014</v>
       </c>
       <c r="I14">
-        <v>1.325481</v>
+        <v>1.3254809999999999</v>
       </c>
       <c r="J14">
-        <v>63.16494845</v>
+        <v>63.164948449999997</v>
       </c>
       <c r="K14" t="s">
         <v>42</v>
@@ -1686,16 +1813,16 @@
         <v>3995</v>
       </c>
       <c r="P14">
-        <v>1533.667084</v>
+        <v>1533.6670839999999</v>
       </c>
       <c r="Q14">
         <v>95</v>
       </c>
       <c r="S14">
-        <v>64.494737</v>
+        <v>64.494737000000001</v>
       </c>
       <c r="T14">
-        <v>2.377972</v>
+        <v>2.3779720000000002</v>
       </c>
       <c r="U14">
         <v>122</v>
@@ -1710,10 +1837,10 @@
         <v>97</v>
       </c>
       <c r="Y14">
-        <v>63.164948</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>63.164948000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1739,10 +1866,10 @@
         <v>3264</v>
       </c>
       <c r="I15">
-        <v>1.402267</v>
+        <v>1.4022669999999999</v>
       </c>
       <c r="J15">
-        <v>77.08860759</v>
+        <v>77.088607589999995</v>
       </c>
       <c r="K15" t="s">
         <v>42</v>
@@ -1766,10 +1893,10 @@
         <v>89</v>
       </c>
       <c r="S15">
-        <v>68.426966</v>
+        <v>68.426965999999993</v>
       </c>
       <c r="T15">
-        <v>1.944505</v>
+        <v>1.9445049999999999</v>
       </c>
       <c r="U15">
         <v>98</v>
@@ -1778,16 +1905,16 @@
         <v>2.14114</v>
       </c>
       <c r="W15">
-        <v>62.142857</v>
+        <v>62.142856999999999</v>
       </c>
       <c r="X15">
         <v>79</v>
       </c>
       <c r="Y15">
-        <v>77.088608</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>77.088607999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1813,10 +1940,10 @@
         <v>3982</v>
       </c>
       <c r="I16">
-        <v>1.497238</v>
+        <v>1.4972380000000001</v>
       </c>
       <c r="J16">
-        <v>54.71296296</v>
+        <v>54.712962959999999</v>
       </c>
       <c r="K16" t="s">
         <v>42</v>
@@ -1840,7 +1967,7 @@
         <v>110</v>
       </c>
       <c r="S16">
-        <v>53.718182</v>
+        <v>53.718181999999999</v>
       </c>
       <c r="T16">
         <v>1.845018</v>
@@ -1849,19 +1976,19 @@
         <v>144</v>
       </c>
       <c r="V16">
-        <v>2.415297</v>
+        <v>2.4152969999999998</v>
       </c>
       <c r="W16">
-        <v>41.034722</v>
+        <v>41.034722000000002</v>
       </c>
       <c r="X16">
         <v>108</v>
       </c>
       <c r="Y16">
-        <v>54.712963</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>54.712963000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1887,7 +2014,7 @@
         <v>3023</v>
       </c>
       <c r="I17">
-        <v>1.697321</v>
+        <v>1.6973210000000001</v>
       </c>
       <c r="J17">
         <v>34.6416185</v>
@@ -1914,16 +2041,16 @@
         <v>198</v>
       </c>
       <c r="S17">
-        <v>30.267677</v>
+        <v>30.267676999999999</v>
       </c>
       <c r="T17">
-        <v>3.858897</v>
+        <v>3.8588969999999998</v>
       </c>
       <c r="U17">
         <v>214</v>
       </c>
       <c r="V17">
-        <v>4.170727</v>
+        <v>4.1707270000000003</v>
       </c>
       <c r="W17">
         <v>28.004673</v>
@@ -1932,10 +2059,10 @@
         <v>173</v>
       </c>
       <c r="Y17">
-        <v>34.641619</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>34.641618999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1961,7 +2088,7 @@
         <v>3583</v>
       </c>
       <c r="I18">
-        <v>1.454368</v>
+        <v>1.4543680000000001</v>
       </c>
       <c r="J18">
         <v>59.25961538</v>
@@ -1988,28 +2115,28 @@
         <v>106</v>
       </c>
       <c r="S18">
-        <v>58.141509</v>
+        <v>58.141508999999999</v>
       </c>
       <c r="T18">
-        <v>2.034159</v>
+        <v>2.0341589999999998</v>
       </c>
       <c r="U18">
         <v>133</v>
       </c>
       <c r="V18">
-        <v>2.552293</v>
+        <v>2.5522930000000001</v>
       </c>
       <c r="W18">
-        <v>46.338346</v>
+        <v>46.338346000000001</v>
       </c>
       <c r="X18">
         <v>104</v>
       </c>
       <c r="Y18">
-        <v>59.259615</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>59.259614999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2056,7 +2183,7 @@
         <v>4824</v>
       </c>
       <c r="P19">
-        <v>1346.393035</v>
+        <v>1346.3930350000001</v>
       </c>
       <c r="Q19">
         <v>62</v>
@@ -2065,16 +2192,16 @@
         <v>104.758065</v>
       </c>
       <c r="T19">
-        <v>1.28524</v>
+        <v>1.2852399999999999</v>
       </c>
       <c r="U19">
         <v>70</v>
       </c>
       <c r="V19">
-        <v>1.451078</v>
+        <v>1.4510780000000001</v>
       </c>
       <c r="W19">
-        <v>92.785714</v>
+        <v>92.785713999999999</v>
       </c>
       <c r="X19">
         <v>60</v>
@@ -2083,7 +2210,7 @@
         <v>108.25</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2109,10 +2236,10 @@
         <v>3274</v>
       </c>
       <c r="I20">
-        <v>1.677153</v>
+        <v>1.6771529999999999</v>
       </c>
       <c r="J20">
-        <v>57.6952381</v>
+        <v>57.695238099999997</v>
       </c>
       <c r="K20" t="s">
         <v>42</v>
@@ -2130,34 +2257,34 @@
         <v>5491</v>
       </c>
       <c r="P20">
-        <v>1103.25988</v>
+        <v>1103.2598800000001</v>
       </c>
       <c r="Q20">
         <v>120</v>
       </c>
       <c r="S20">
-        <v>50.483333</v>
+        <v>50.483333000000002</v>
       </c>
       <c r="T20">
-        <v>2.185394</v>
+        <v>2.1853940000000001</v>
       </c>
       <c r="U20">
         <v>129</v>
       </c>
       <c r="V20">
-        <v>2.349299</v>
+        <v>2.3492989999999998</v>
       </c>
       <c r="W20">
-        <v>46.96124</v>
+        <v>46.961239999999997</v>
       </c>
       <c r="X20">
         <v>105</v>
       </c>
       <c r="Y20">
-        <v>57.695238</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>57.695238000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2183,7 +2310,7 @@
         <v>2570</v>
       </c>
       <c r="I21">
-        <v>1.462646</v>
+        <v>1.4626459999999999</v>
       </c>
       <c r="J21">
         <v>39.55769231</v>
@@ -2213,25 +2340,25 @@
         <v>35.0625</v>
       </c>
       <c r="T21">
-        <v>4.682096</v>
+        <v>4.6820959999999996</v>
       </c>
       <c r="U21">
         <v>196</v>
       </c>
       <c r="V21">
-        <v>5.214153</v>
+        <v>5.2141529999999996</v>
       </c>
       <c r="W21">
-        <v>31.484694</v>
+        <v>31.484694000000001</v>
       </c>
       <c r="X21">
         <v>156</v>
       </c>
       <c r="Y21">
-        <v>39.557692</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>39.557692000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2260,7 +2387,7 @@
         <v>1.52277</v>
       </c>
       <c r="J22">
-        <v>56.18965517</v>
+        <v>56.189655170000002</v>
       </c>
       <c r="K22" t="s">
         <v>42</v>
@@ -2278,16 +2405,16 @@
         <v>4882</v>
       </c>
       <c r="P22">
-        <v>1335.108562</v>
+        <v>1335.1085619999999</v>
       </c>
       <c r="Q22">
         <v>118</v>
       </c>
       <c r="S22">
-        <v>55.237288</v>
+        <v>55.237287999999999</v>
       </c>
       <c r="T22">
-        <v>2.417042</v>
+        <v>2.4170419999999999</v>
       </c>
       <c r="U22">
         <v>129</v>
@@ -2296,16 +2423,16 @@
         <v>2.64236</v>
       </c>
       <c r="W22">
-        <v>50.527132</v>
+        <v>50.527132000000002</v>
       </c>
       <c r="X22">
         <v>116</v>
       </c>
       <c r="Y22">
-        <v>56.189655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+        <v>56.189655000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2331,10 +2458,10 @@
         <v>575</v>
       </c>
       <c r="I23">
-        <v>1.196522</v>
+        <v>1.1965220000000001</v>
       </c>
       <c r="J23">
-        <v>84.35714286</v>
+        <v>84.357142859999996</v>
       </c>
       <c r="K23" t="s">
         <v>42</v>
@@ -2358,28 +2485,28 @@
         <v>14</v>
       </c>
       <c r="S23">
-        <v>84.357143</v>
+        <v>84.357142999999994</v>
       </c>
       <c r="T23">
-        <v>2.034884</v>
+        <v>2.0348839999999999</v>
       </c>
       <c r="U23">
         <v>14</v>
       </c>
       <c r="V23">
-        <v>2.034884</v>
+        <v>2.0348839999999999</v>
       </c>
       <c r="W23">
-        <v>84.357143</v>
+        <v>84.357142999999994</v>
       </c>
       <c r="X23">
         <v>14</v>
       </c>
       <c r="Y23">
-        <v>84.357143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>84.357142999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2405,10 +2532,10 @@
         <v>3714</v>
       </c>
       <c r="I24">
-        <v>1.773829</v>
+        <v>1.7738290000000001</v>
       </c>
       <c r="J24">
-        <v>57.20754717</v>
+        <v>57.207547169999998</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -2426,34 +2553,34 @@
         <v>6588</v>
       </c>
       <c r="P24">
-        <v>920.461445</v>
+        <v>920.46144500000003</v>
       </c>
       <c r="Q24">
         <v>89</v>
       </c>
       <c r="S24">
-        <v>68.134831</v>
+        <v>68.134831000000005</v>
       </c>
       <c r="T24">
-        <v>1.350941</v>
+        <v>1.3509409999999999</v>
       </c>
       <c r="U24">
         <v>129</v>
       </c>
       <c r="V24">
-        <v>1.958106</v>
+        <v>1.9581059999999999</v>
       </c>
       <c r="W24">
-        <v>47.007752</v>
+        <v>47.007752000000004</v>
       </c>
       <c r="X24">
         <v>106</v>
       </c>
       <c r="Y24">
-        <v>57.207547</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>57.207546999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2479,10 +2606,10 @@
         <v>3612</v>
       </c>
       <c r="I25">
-        <v>1.469823</v>
+        <v>1.4698230000000001</v>
       </c>
       <c r="J25">
-        <v>35.95977011</v>
+        <v>35.959770110000001</v>
       </c>
       <c r="K25" t="s">
         <v>42</v>
@@ -2506,28 +2633,28 @@
         <v>156</v>
       </c>
       <c r="S25">
-        <v>40.108974</v>
+        <v>40.108974000000003</v>
       </c>
       <c r="T25">
-        <v>2.938406</v>
+        <v>2.9384060000000001</v>
       </c>
       <c r="U25">
         <v>201</v>
       </c>
       <c r="V25">
-        <v>3.786024</v>
+        <v>3.7860239999999998</v>
       </c>
       <c r="W25">
-        <v>31.129353</v>
+        <v>31.129352999999998</v>
       </c>
       <c r="X25">
         <v>174</v>
       </c>
       <c r="Y25">
-        <v>35.95977</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>35.959769999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2553,7 +2680,7 @@
         <v>4251</v>
       </c>
       <c r="I26">
-        <v>1.649965</v>
+        <v>1.6499649999999999</v>
       </c>
       <c r="J26">
         <v>20.93333333</v>
@@ -2574,7 +2701,7 @@
         <v>7014</v>
       </c>
       <c r="P26">
-        <v>850.584545</v>
+        <v>850.58454500000005</v>
       </c>
       <c r="Q26">
         <v>314</v>
@@ -2583,25 +2710,25 @@
         <v>19</v>
       </c>
       <c r="T26">
-        <v>4.476761</v>
+        <v>4.4767609999999998</v>
       </c>
       <c r="U26">
         <v>353</v>
       </c>
       <c r="V26">
-        <v>5.032792</v>
+        <v>5.0327919999999997</v>
       </c>
       <c r="W26">
-        <v>16.90085</v>
+        <v>16.900849999999998</v>
       </c>
       <c r="X26">
         <v>285</v>
       </c>
       <c r="Y26">
-        <v>20.933333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+        <v>20.933333000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2651,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2701,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2751,7 +2878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2801,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2830,7 +2957,7 @@
         <v>1.289164</v>
       </c>
       <c r="J31">
-        <v>67.07</v>
+        <v>67.069999999999993</v>
       </c>
       <c r="K31" t="s">
         <v>42</v>
@@ -2848,34 +2975,34 @@
         <v>4378</v>
       </c>
       <c r="P31">
-        <v>1531.978072</v>
+        <v>1531.9780720000001</v>
       </c>
       <c r="Q31">
         <v>103</v>
       </c>
       <c r="S31">
-        <v>65.116505</v>
+        <v>65.116505000000004</v>
       </c>
       <c r="T31">
-        <v>2.352672</v>
+        <v>2.3526720000000001</v>
       </c>
       <c r="U31">
         <v>110</v>
       </c>
       <c r="V31">
-        <v>2.512563</v>
+        <v>2.5125630000000001</v>
       </c>
       <c r="W31">
-        <v>60.972727</v>
+        <v>60.972726999999999</v>
       </c>
       <c r="X31">
         <v>100</v>
       </c>
       <c r="Y31">
-        <v>67.07</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+        <v>67.069999999999993</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2904,7 +3031,7 @@
         <v>1.477935</v>
       </c>
       <c r="J32">
-        <v>9.67572156</v>
+        <v>9.6757215599999995</v>
       </c>
       <c r="K32" t="s">
         <v>42</v>
@@ -2928,28 +3055,28 @@
         <v>501</v>
       </c>
       <c r="S32">
-        <v>11.37525</v>
+        <v>11.375249999999999</v>
       </c>
       <c r="T32">
-        <v>5.775882</v>
+        <v>5.7758820000000002</v>
       </c>
       <c r="U32">
         <v>716</v>
       </c>
       <c r="V32">
-        <v>8.254554</v>
+        <v>8.2545540000000006</v>
       </c>
       <c r="W32">
-        <v>7.959497</v>
+        <v>7.9594969999999998</v>
       </c>
       <c r="X32">
         <v>589</v>
       </c>
       <c r="Y32">
-        <v>9.675722</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+        <v>9.6757220000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2978,7 +3105,7 @@
         <v>1.892023</v>
       </c>
       <c r="J33">
-        <v>70.87878788</v>
+        <v>70.878787880000004</v>
       </c>
       <c r="K33" t="s">
         <v>42</v>
@@ -2996,25 +3123,25 @@
         <v>4696</v>
       </c>
       <c r="P33">
-        <v>1494.250426</v>
+        <v>1494.2504260000001</v>
       </c>
       <c r="Q33">
         <v>103</v>
       </c>
       <c r="S33">
-        <v>68.126214</v>
+        <v>68.126214000000004</v>
       </c>
       <c r="T33">
-        <v>2.193356</v>
+        <v>2.1933560000000001</v>
       </c>
       <c r="U33">
         <v>113</v>
       </c>
       <c r="V33">
-        <v>2.406303</v>
+        <v>2.4063029999999999</v>
       </c>
       <c r="W33">
-        <v>62.097345</v>
+        <v>62.097344999999997</v>
       </c>
       <c r="X33">
         <v>99</v>
@@ -3023,7 +3150,7 @@
         <v>70.878788</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -3049,10 +3176,10 @@
         <v>2592</v>
       </c>
       <c r="I34">
-        <v>1.532407</v>
+        <v>1.5324070000000001</v>
       </c>
       <c r="J34">
-        <v>68.50943396</v>
+        <v>68.509433959999996</v>
       </c>
       <c r="K34" t="s">
         <v>42</v>
@@ -3070,34 +3197,34 @@
         <v>3972</v>
       </c>
       <c r="P34">
-        <v>1828.298087</v>
+        <v>1828.2980869999999</v>
       </c>
       <c r="Q34">
         <v>109</v>
       </c>
       <c r="S34">
-        <v>66.623853</v>
+        <v>66.623852999999997</v>
       </c>
       <c r="T34">
-        <v>2.744209</v>
+        <v>2.7442090000000001</v>
       </c>
       <c r="U34">
         <v>120</v>
       </c>
       <c r="V34">
-        <v>3.021148</v>
+        <v>3.0211480000000002</v>
       </c>
       <c r="W34">
-        <v>60.516667</v>
+        <v>60.516666999999998</v>
       </c>
       <c r="X34">
         <v>106</v>
       </c>
       <c r="Y34">
-        <v>68.509434</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+        <v>68.509433999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3144,13 +3271,13 @@
         <v>6023</v>
       </c>
       <c r="P35">
-        <v>968.454259</v>
+        <v>968.45425899999998</v>
       </c>
       <c r="Q35">
         <v>116</v>
       </c>
       <c r="S35">
-        <v>50.284483</v>
+        <v>50.284483000000002</v>
       </c>
       <c r="T35">
         <v>1.925951</v>
@@ -3162,7 +3289,7 @@
         <v>2.805911</v>
       </c>
       <c r="W35">
-        <v>34.514793</v>
+        <v>34.514792999999997</v>
       </c>
       <c r="X35">
         <v>121</v>
@@ -3171,7 +3298,7 @@
         <v>48.206612</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3200,7 +3327,7 @@
         <v>1.894347</v>
       </c>
       <c r="J36">
-        <v>42.37226277</v>
+        <v>42.372262769999999</v>
       </c>
       <c r="K36" t="s">
         <v>42</v>
@@ -3218,16 +3345,16 @@
         <v>5630</v>
       </c>
       <c r="P36">
-        <v>1031.083481</v>
+        <v>1031.0834809999999</v>
       </c>
       <c r="Q36">
         <v>143</v>
       </c>
       <c r="S36">
-        <v>40.594406</v>
+        <v>40.594405999999999</v>
       </c>
       <c r="T36">
-        <v>2.539964</v>
+        <v>2.5399639999999999</v>
       </c>
       <c r="U36">
         <v>209</v>
@@ -3236,16 +3363,16 @@
         <v>3.712256</v>
       </c>
       <c r="W36">
-        <v>27.77512</v>
+        <v>27.775120000000001</v>
       </c>
       <c r="X36">
         <v>137</v>
       </c>
       <c r="Y36">
-        <v>42.372263</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
+        <v>42.372262999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3271,10 +3398,10 @@
         <v>2461</v>
       </c>
       <c r="I37">
-        <v>1.280374</v>
+        <v>1.2803739999999999</v>
       </c>
       <c r="J37">
-        <v>71.44444444</v>
+        <v>71.444444439999998</v>
       </c>
       <c r="K37" t="s">
         <v>42</v>
@@ -3292,13 +3419,13 @@
         <v>3151</v>
       </c>
       <c r="P37">
-        <v>2040.622025</v>
+        <v>2040.6220249999999</v>
       </c>
       <c r="Q37">
         <v>87</v>
       </c>
       <c r="S37">
-        <v>73.908046</v>
+        <v>73.908045999999999</v>
       </c>
       <c r="T37">
         <v>2.761028</v>
@@ -3307,19 +3434,19 @@
         <v>105</v>
       </c>
       <c r="V37">
-        <v>3.332275</v>
+        <v>3.3322750000000001</v>
       </c>
       <c r="W37">
-        <v>61.238095</v>
+        <v>61.238095000000001</v>
       </c>
       <c r="X37">
         <v>90</v>
       </c>
       <c r="Y37">
-        <v>71.444444</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25">
+        <v>71.444444000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3348,7 +3475,7 @@
         <v>1.86016</v>
       </c>
       <c r="J38">
-        <v>48.45454545</v>
+        <v>48.454545449999998</v>
       </c>
       <c r="K38" t="s">
         <v>42</v>
@@ -3372,28 +3499,28 @@
         <v>98</v>
       </c>
       <c r="S38">
-        <v>48.94898</v>
+        <v>48.948979999999999</v>
       </c>
       <c r="T38">
-        <v>2.47225</v>
+        <v>2.4722499999999998</v>
       </c>
       <c r="U38">
         <v>124</v>
       </c>
       <c r="V38">
-        <v>3.128153</v>
+        <v>3.1281530000000002</v>
       </c>
       <c r="W38">
-        <v>38.685484</v>
+        <v>38.685484000000002</v>
       </c>
       <c r="X38">
         <v>99</v>
       </c>
       <c r="Y38">
-        <v>48.454545</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
+        <v>48.454545000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3446,19 +3573,19 @@
         <v>71</v>
       </c>
       <c r="S39">
-        <v>69.521127</v>
+        <v>69.521127000000007</v>
       </c>
       <c r="T39">
-        <v>2.030312</v>
+        <v>2.0303119999999999</v>
       </c>
       <c r="U39">
         <v>115</v>
       </c>
       <c r="V39">
-        <v>3.288533</v>
+        <v>3.2885330000000002</v>
       </c>
       <c r="W39">
-        <v>42.921739</v>
+        <v>42.921739000000002</v>
       </c>
       <c r="X39">
         <v>100</v>
@@ -3467,7 +3594,7 @@
         <v>49.36</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3493,7 +3620,7 @@
         <v>2982</v>
       </c>
       <c r="I40">
-        <v>1.64118</v>
+        <v>1.6411800000000001</v>
       </c>
       <c r="J40">
         <v>19.97379913</v>
@@ -3514,25 +3641,25 @@
         <v>4894</v>
       </c>
       <c r="P40">
-        <v>934.613813</v>
+        <v>934.61381300000005</v>
       </c>
       <c r="Q40">
         <v>235</v>
       </c>
       <c r="S40">
-        <v>19.46383</v>
+        <v>19.463830000000002</v>
       </c>
       <c r="T40">
-        <v>4.801798</v>
+        <v>4.8017979999999998</v>
       </c>
       <c r="U40">
         <v>279</v>
       </c>
       <c r="V40">
-        <v>5.700858</v>
+        <v>5.7008580000000002</v>
       </c>
       <c r="W40">
-        <v>16.394265</v>
+        <v>16.394265000000001</v>
       </c>
       <c r="X40">
         <v>229</v>
@@ -3541,7 +3668,7 @@
         <v>19.973799</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3567,10 +3694,10 @@
         <v>1140</v>
       </c>
       <c r="I41">
-        <v>1.637719</v>
+        <v>1.6377189999999999</v>
       </c>
       <c r="J41">
-        <v>51.89795918</v>
+        <v>51.897959180000001</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -3588,7 +3715,7 @@
         <v>1867</v>
       </c>
       <c r="P41">
-        <v>1362.0782</v>
+        <v>1362.0781999999999</v>
       </c>
       <c r="Q41">
         <v>45</v>
@@ -3597,16 +3724,16 @@
         <v>56.511111</v>
       </c>
       <c r="T41">
-        <v>2.410284</v>
+        <v>2.4102839999999999</v>
       </c>
       <c r="U41">
         <v>55</v>
       </c>
       <c r="V41">
-        <v>2.945903</v>
+        <v>2.9459029999999999</v>
       </c>
       <c r="W41">
-        <v>46.236364</v>
+        <v>46.236364000000002</v>
       </c>
       <c r="X41">
         <v>49</v>
@@ -3615,7 +3742,7 @@
         <v>51.897959</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3641,10 +3768,10 @@
         <v>1138</v>
       </c>
       <c r="I42">
-        <v>1.250439</v>
+        <v>1.2504390000000001</v>
       </c>
       <c r="J42">
-        <v>49.94117647</v>
+        <v>49.941176470000002</v>
       </c>
       <c r="K42" t="s">
         <v>42</v>
@@ -3662,34 +3789,34 @@
         <v>1423</v>
       </c>
       <c r="P42">
-        <v>1789.880534</v>
+        <v>1789.8805339999999</v>
       </c>
       <c r="Q42">
         <v>39</v>
       </c>
       <c r="S42">
-        <v>65.307692</v>
+        <v>65.307692000000003</v>
       </c>
       <c r="T42">
-        <v>2.740689</v>
+        <v>2.7406890000000002</v>
       </c>
       <c r="U42">
         <v>47</v>
       </c>
       <c r="V42">
-        <v>3.302881</v>
+        <v>3.3028810000000002</v>
       </c>
       <c r="W42">
-        <v>54.191489</v>
+        <v>54.191488999999997</v>
       </c>
       <c r="X42">
         <v>51</v>
       </c>
       <c r="Y42">
-        <v>49.941176</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25">
+        <v>49.941175999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3718,7 +3845,7 @@
         <v>1.394444</v>
       </c>
       <c r="J43">
-        <v>42.93103448</v>
+        <v>42.931034480000001</v>
       </c>
       <c r="K43" t="s">
         <v>42</v>
@@ -3742,28 +3869,28 @@
         <v>55</v>
       </c>
       <c r="S43">
-        <v>45.272727</v>
+        <v>45.272727000000003</v>
       </c>
       <c r="T43">
-        <v>2.739044</v>
+        <v>2.7390439999999998</v>
       </c>
       <c r="U43">
         <v>76</v>
       </c>
       <c r="V43">
-        <v>3.784861</v>
+        <v>3.7848609999999998</v>
       </c>
       <c r="W43">
-        <v>32.763158</v>
+        <v>32.763157999999997</v>
       </c>
       <c r="X43">
         <v>58</v>
       </c>
       <c r="Y43">
-        <v>42.931034</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
+        <v>42.931033999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -3816,7 +3943,7 @@
         <v>42</v>
       </c>
       <c r="S44">
-        <v>33.928571</v>
+        <v>33.928570999999998</v>
       </c>
       <c r="T44">
         <v>2.8</v>
@@ -3825,7 +3952,7 @@
         <v>59</v>
       </c>
       <c r="V44">
-        <v>3.933333</v>
+        <v>3.9333330000000002</v>
       </c>
       <c r="W44">
         <v>24.152542</v>
@@ -3834,10 +3961,10 @@
         <v>52</v>
       </c>
       <c r="Y44">
-        <v>27.403846</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25">
+        <v>27.403846000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -3863,10 +3990,10 @@
         <v>749</v>
       </c>
       <c r="I45">
-        <v>1.249666</v>
+        <v>1.2496659999999999</v>
       </c>
       <c r="J45">
-        <v>67.40909091</v>
+        <v>67.409090910000003</v>
       </c>
       <c r="K45" t="s">
         <v>42</v>
@@ -3890,7 +4017,7 @@
         <v>23</v>
       </c>
       <c r="S45">
-        <v>64.478261</v>
+        <v>64.478261000000003</v>
       </c>
       <c r="T45">
         <v>2.457265</v>
@@ -3899,30 +4026,2059 @@
         <v>26</v>
       </c>
       <c r="V45">
-        <v>2.777778</v>
+        <v>2.7777780000000001</v>
       </c>
       <c r="W45">
-        <v>57.038462</v>
+        <v>57.038462000000003</v>
       </c>
       <c r="X45">
         <v>22</v>
       </c>
       <c r="Y45">
-        <v>67.409091</v>
+        <v>67.409091000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>55</v>
+      </c>
+      <c r="G46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46">
+        <v>2414</v>
+      </c>
+      <c r="I46">
+        <v>1.6553439999999999</v>
+      </c>
+      <c r="J46">
+        <v>125.14545455</v>
+      </c>
+      <c r="K46" t="s">
+        <v>42</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>6883</v>
+      </c>
+      <c r="N46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O46">
+        <v>3996</v>
+      </c>
+      <c r="P46">
+        <v>1722.4724719999999</v>
+      </c>
+      <c r="Q46">
+        <v>72</v>
+      </c>
+      <c r="S46">
+        <v>95.597222000000002</v>
+      </c>
+      <c r="T46">
+        <v>1.8018019999999999</v>
+      </c>
+      <c r="U46">
+        <v>86</v>
+      </c>
+      <c r="V46">
+        <v>2.1521520000000001</v>
+      </c>
+      <c r="W46">
+        <v>80.034884000000005</v>
+      </c>
+      <c r="X46">
+        <v>55</v>
+      </c>
+      <c r="Y46">
+        <v>125.145455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>112</v>
+      </c>
+      <c r="G47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47">
+        <v>1946</v>
+      </c>
+      <c r="I47">
+        <v>1.308325</v>
+      </c>
+      <c r="J47">
+        <v>45.0625</v>
+      </c>
+      <c r="K47" t="s">
+        <v>42</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>5047</v>
+      </c>
+      <c r="N47" t="s">
+        <v>140</v>
+      </c>
+      <c r="O47">
+        <v>2546</v>
+      </c>
+      <c r="P47">
+        <v>1982.325216</v>
+      </c>
+      <c r="Q47">
+        <v>112</v>
+      </c>
+      <c r="S47">
+        <v>45.0625</v>
+      </c>
+      <c r="T47">
+        <v>4.399057</v>
+      </c>
+      <c r="U47">
+        <v>118</v>
+      </c>
+      <c r="V47">
+        <v>4.6347209999999999</v>
+      </c>
+      <c r="W47">
+        <v>42.771186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>59</v>
+      </c>
+      <c r="G48" t="s">
+        <v>41</v>
+      </c>
+      <c r="H48">
+        <v>2414</v>
+      </c>
+      <c r="I48">
+        <v>1.5700080000000001</v>
+      </c>
+      <c r="J48">
+        <v>102.72881356000001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>42</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>6061</v>
+      </c>
+      <c r="N48" t="s">
+        <v>136</v>
+      </c>
+      <c r="O48">
+        <v>3790</v>
+      </c>
+      <c r="P48">
+        <v>1599.208443</v>
+      </c>
+      <c r="Q48">
+        <v>75</v>
+      </c>
+      <c r="S48">
+        <v>80.813333</v>
+      </c>
+      <c r="T48">
+        <v>1.9788920000000001</v>
+      </c>
+      <c r="U48">
+        <v>81</v>
+      </c>
+      <c r="V48">
+        <v>2.137203</v>
+      </c>
+      <c r="W48">
+        <v>74.827160000000006</v>
+      </c>
+      <c r="X48">
+        <v>59</v>
+      </c>
+      <c r="Y48">
+        <v>102.728814</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s">
+        <v>30</v>
+      </c>
+      <c r="H49">
+        <v>3350</v>
+      </c>
+      <c r="I49">
+        <v>1.8934329999999999</v>
+      </c>
+      <c r="J49">
+        <v>61.46052632</v>
+      </c>
+      <c r="K49" t="s">
+        <v>42</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>4671</v>
+      </c>
+      <c r="N49" t="s">
+        <v>127</v>
+      </c>
+      <c r="O49">
+        <v>6343</v>
+      </c>
+      <c r="P49">
+        <v>736.402333</v>
+      </c>
+      <c r="Q49">
+        <v>76</v>
+      </c>
+      <c r="S49">
+        <v>61.460526000000002</v>
+      </c>
+      <c r="T49">
+        <v>1.1981710000000001</v>
+      </c>
+      <c r="U49">
+        <v>79</v>
+      </c>
+      <c r="V49">
+        <v>1.2454670000000001</v>
+      </c>
+      <c r="W49">
+        <v>59.126581999999999</v>
+      </c>
+      <c r="X49">
+        <v>54</v>
+      </c>
+      <c r="Y49">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>42</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>136</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>107</v>
+      </c>
+      <c r="G51" t="s">
+        <v>41</v>
+      </c>
+      <c r="H51">
+        <v>2249</v>
+      </c>
+      <c r="I51">
+        <v>1.467319</v>
+      </c>
+      <c r="J51">
+        <v>60.028037380000001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>6423</v>
+      </c>
+      <c r="N51" t="s">
+        <v>63</v>
+      </c>
+      <c r="O51">
+        <v>3300</v>
+      </c>
+      <c r="P51">
+        <v>1946.363636</v>
+      </c>
+      <c r="Q51">
+        <v>93</v>
+      </c>
+      <c r="S51">
+        <v>69.064515999999998</v>
+      </c>
+      <c r="T51">
+        <v>2.8181820000000002</v>
+      </c>
+      <c r="U51">
+        <v>121</v>
+      </c>
+      <c r="V51">
+        <v>3.6666669999999999</v>
+      </c>
+      <c r="W51">
+        <v>53.082644999999999</v>
+      </c>
+      <c r="X51">
+        <v>107</v>
+      </c>
+      <c r="Y51">
+        <v>60.028036999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>464</v>
+      </c>
+      <c r="G52" t="s">
+        <v>41</v>
+      </c>
+      <c r="H52">
+        <v>7559</v>
+      </c>
+      <c r="I52">
+        <v>1.5184550000000001</v>
+      </c>
+      <c r="J52">
+        <v>51.808189659999996</v>
+      </c>
+      <c r="K52" t="s">
+        <v>42</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>24039</v>
+      </c>
+      <c r="N52" t="s">
+        <v>133</v>
+      </c>
+      <c r="O52">
+        <v>11478</v>
+      </c>
+      <c r="P52">
+        <v>2094.354417</v>
+      </c>
+      <c r="Q52">
+        <v>474</v>
+      </c>
+      <c r="S52">
+        <v>50.71519</v>
+      </c>
+      <c r="T52">
+        <v>4.1296390000000001</v>
+      </c>
+      <c r="U52">
+        <v>542</v>
+      </c>
+      <c r="V52">
+        <v>4.7220769999999996</v>
+      </c>
+      <c r="W52">
+        <v>44.352398999999998</v>
+      </c>
+      <c r="X52">
+        <v>464</v>
+      </c>
+      <c r="Y52">
+        <v>51.808190000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>83</v>
+      </c>
+      <c r="G53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53">
+        <v>2993</v>
+      </c>
+      <c r="I53">
+        <v>1.6267959999999999</v>
+      </c>
+      <c r="J53">
+        <v>70.337349399999994</v>
+      </c>
+      <c r="K53" t="s">
+        <v>42</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>5838</v>
+      </c>
+      <c r="N53" t="s">
+        <v>131</v>
+      </c>
+      <c r="O53">
+        <v>4869</v>
+      </c>
+      <c r="P53">
+        <v>1199.014171</v>
+      </c>
+      <c r="Q53">
+        <v>127</v>
+      </c>
+      <c r="S53">
+        <v>45.968504000000003</v>
+      </c>
+      <c r="T53">
+        <v>2.6083379999999998</v>
+      </c>
+      <c r="U53">
+        <v>134</v>
+      </c>
+      <c r="V53">
+        <v>2.7521049999999998</v>
+      </c>
+      <c r="W53">
+        <v>43.567163999999998</v>
+      </c>
+      <c r="X53">
+        <v>83</v>
+      </c>
+      <c r="Y53">
+        <v>70.337349000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54">
+        <v>83</v>
+      </c>
+      <c r="G54" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54">
+        <v>3504</v>
+      </c>
+      <c r="I54">
+        <v>1.686644</v>
+      </c>
+      <c r="J54">
+        <v>66.04819277</v>
+      </c>
+      <c r="K54" t="s">
+        <v>42</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>5482</v>
+      </c>
+      <c r="N54" t="s">
+        <v>129</v>
+      </c>
+      <c r="O54">
+        <v>5910</v>
+      </c>
+      <c r="P54">
+        <v>927.58037200000001</v>
+      </c>
+      <c r="Q54">
+        <v>83</v>
+      </c>
+      <c r="S54">
+        <v>66.048192999999998</v>
+      </c>
+      <c r="T54">
+        <v>1.404399</v>
+      </c>
+      <c r="U54">
+        <v>110</v>
+      </c>
+      <c r="V54">
+        <v>1.8612519999999999</v>
+      </c>
+      <c r="W54">
+        <v>49.836364000000003</v>
+      </c>
+      <c r="X54">
+        <v>72</v>
+      </c>
+      <c r="Y54">
+        <v>76.138889000000006</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55">
+        <v>2049</v>
+      </c>
+      <c r="I55">
+        <v>1.2942899999999999</v>
+      </c>
+      <c r="J55">
+        <v>45.756521739999997</v>
+      </c>
+      <c r="K55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>5262</v>
+      </c>
+      <c r="N55" t="s">
+        <v>127</v>
+      </c>
+      <c r="O55">
+        <v>2652</v>
+      </c>
+      <c r="P55">
+        <v>1984.162896</v>
+      </c>
+      <c r="Q55">
+        <v>115</v>
+      </c>
+      <c r="S55">
+        <v>45.756521999999997</v>
+      </c>
+      <c r="T55">
+        <v>4.3363500000000004</v>
+      </c>
+      <c r="U55">
+        <v>130</v>
+      </c>
+      <c r="V55">
+        <v>4.901961</v>
+      </c>
+      <c r="W55">
+        <v>40.476922999999999</v>
+      </c>
+      <c r="X55">
+        <v>106</v>
+      </c>
+      <c r="Y55">
+        <v>49.641508999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>120</v>
+      </c>
+      <c r="G56" t="s">
+        <v>30</v>
+      </c>
+      <c r="H56">
+        <v>2046</v>
+      </c>
+      <c r="I56">
+        <v>1.365591</v>
+      </c>
+      <c r="J56">
+        <v>43.266666669999999</v>
+      </c>
+      <c r="K56" t="s">
+        <v>42</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>5192</v>
+      </c>
+      <c r="N56" t="s">
+        <v>114</v>
+      </c>
+      <c r="O56">
+        <v>2794</v>
+      </c>
+      <c r="P56">
+        <v>1858.2677169999999</v>
+      </c>
+      <c r="Q56">
+        <v>120</v>
+      </c>
+      <c r="S56">
+        <v>43.266666999999998</v>
+      </c>
+      <c r="T56">
+        <v>4.294918</v>
+      </c>
+      <c r="U56">
+        <v>127</v>
+      </c>
+      <c r="V56">
+        <v>4.5454549999999996</v>
+      </c>
+      <c r="W56">
+        <v>40.881889999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
+        <v>30</v>
+      </c>
+      <c r="H57">
+        <v>3145</v>
+      </c>
+      <c r="I57">
+        <v>1.537361</v>
+      </c>
+      <c r="J57">
+        <v>70.731707319999998</v>
+      </c>
+      <c r="K57" t="s">
+        <v>42</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>5800</v>
+      </c>
+      <c r="N57" t="s">
+        <v>124</v>
+      </c>
+      <c r="O57">
+        <v>4835</v>
+      </c>
+      <c r="P57">
+        <v>1199.58635</v>
+      </c>
+      <c r="Q57">
+        <v>82</v>
+      </c>
+      <c r="S57">
+        <v>70.731707</v>
+      </c>
+      <c r="T57">
+        <v>1.695967</v>
+      </c>
+      <c r="U57">
+        <v>87</v>
+      </c>
+      <c r="V57">
+        <v>1.79938</v>
+      </c>
+      <c r="W57">
+        <v>66.666667000000004</v>
+      </c>
+      <c r="X57">
+        <v>52</v>
+      </c>
+      <c r="Y57">
+        <v>111.538462</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58">
+        <v>215</v>
+      </c>
+      <c r="G58" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58">
+        <v>2549</v>
+      </c>
+      <c r="I58">
+        <v>1.2499020000000001</v>
+      </c>
+      <c r="J58">
+        <v>22.70232558</v>
+      </c>
+      <c r="K58" t="s">
+        <v>42</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>4881</v>
+      </c>
+      <c r="N58" t="s">
+        <v>105</v>
+      </c>
+      <c r="O58">
+        <v>3186</v>
+      </c>
+      <c r="P58">
+        <v>1532.0150659999999</v>
+      </c>
+      <c r="Q58">
+        <v>215</v>
+      </c>
+      <c r="S58">
+        <v>22.702325999999999</v>
+      </c>
+      <c r="T58">
+        <v>6.7482740000000003</v>
+      </c>
+      <c r="U58">
+        <v>226</v>
+      </c>
+      <c r="V58">
+        <v>7.093534</v>
+      </c>
+      <c r="W58">
+        <v>21.597345000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>173</v>
+      </c>
+      <c r="G59" t="s">
+        <v>30</v>
+      </c>
+      <c r="H59">
+        <v>2715</v>
+      </c>
+      <c r="I59">
+        <v>1.546961</v>
+      </c>
+      <c r="J59">
+        <v>31.838150290000002</v>
+      </c>
+      <c r="K59" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>5508</v>
+      </c>
+      <c r="N59" t="s">
+        <v>121</v>
+      </c>
+      <c r="O59">
+        <v>4200</v>
+      </c>
+      <c r="P59">
+        <v>1311.4285709999999</v>
+      </c>
+      <c r="Q59">
+        <v>173</v>
+      </c>
+      <c r="S59">
+        <v>31.838149999999999</v>
+      </c>
+      <c r="T59">
+        <v>4.1190480000000003</v>
+      </c>
+      <c r="U59">
+        <v>196</v>
+      </c>
+      <c r="V59">
+        <v>4.6666670000000003</v>
+      </c>
+      <c r="W59">
+        <v>28.102041</v>
+      </c>
+      <c r="X59">
+        <v>162</v>
+      </c>
+      <c r="Y59">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60">
+        <v>363</v>
+      </c>
+      <c r="G60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60">
+        <v>3996</v>
+      </c>
+      <c r="I60">
+        <v>1.774024</v>
+      </c>
+      <c r="J60">
+        <v>16.68870523</v>
+      </c>
+      <c r="K60" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>6058</v>
+      </c>
+      <c r="N60" t="s">
+        <v>81</v>
+      </c>
+      <c r="O60">
+        <v>7089</v>
+      </c>
+      <c r="P60">
+        <v>854.56340799999998</v>
+      </c>
+      <c r="Q60">
+        <v>393</v>
+      </c>
+      <c r="S60">
+        <v>15.414758000000001</v>
+      </c>
+      <c r="T60">
+        <v>5.5438000000000001</v>
+      </c>
+      <c r="U60">
+        <v>504</v>
+      </c>
+      <c r="V60">
+        <v>7.1096060000000003</v>
+      </c>
+      <c r="W60">
+        <v>12.019841</v>
+      </c>
+      <c r="X60">
+        <v>363</v>
+      </c>
+      <c r="Y60">
+        <v>16.688704999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>98</v>
+      </c>
+      <c r="G61" t="s">
+        <v>30</v>
+      </c>
+      <c r="H61">
+        <v>2369</v>
+      </c>
+      <c r="I61">
+        <v>1.383284</v>
+      </c>
+      <c r="J61">
+        <v>52.122448980000001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>5108</v>
+      </c>
+      <c r="N61" t="s">
+        <v>114</v>
+      </c>
+      <c r="O61">
+        <v>3277</v>
+      </c>
+      <c r="P61">
+        <v>1558.742753</v>
+      </c>
+      <c r="Q61">
+        <v>98</v>
+      </c>
+      <c r="S61">
+        <v>52.122449000000003</v>
+      </c>
+      <c r="T61">
+        <v>2.9905400000000002</v>
+      </c>
+      <c r="U61">
+        <v>112</v>
+      </c>
+      <c r="V61">
+        <v>3.4177599999999999</v>
+      </c>
+      <c r="W61">
+        <v>45.607143000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>48</v>
+      </c>
+      <c r="G62" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62">
+        <v>1438</v>
+      </c>
+      <c r="I62">
+        <v>1.212796</v>
+      </c>
+      <c r="J62">
+        <v>62.0625</v>
+      </c>
+      <c r="K62" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>2979</v>
+      </c>
+      <c r="N62" t="s">
+        <v>118</v>
+      </c>
+      <c r="O62">
+        <v>1744</v>
+      </c>
+      <c r="P62">
+        <v>1708.142202</v>
+      </c>
+      <c r="Q62">
+        <v>48</v>
+      </c>
+      <c r="S62">
+        <v>62.0625</v>
+      </c>
+      <c r="T62">
+        <v>2.752294</v>
+      </c>
+      <c r="U62">
+        <v>62</v>
+      </c>
+      <c r="V62">
+        <v>3.5550459999999999</v>
+      </c>
+      <c r="W62">
+        <v>48.048386999999998</v>
+      </c>
+      <c r="X62">
+        <v>44</v>
+      </c>
+      <c r="Y62">
+        <v>67.704544999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>117</v>
+      </c>
+      <c r="D63" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>144</v>
+      </c>
+      <c r="G63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63">
+        <v>2738</v>
+      </c>
+      <c r="I63">
+        <v>1.694302</v>
+      </c>
+      <c r="J63">
+        <v>43.055555560000002</v>
+      </c>
+      <c r="K63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>6200</v>
+      </c>
+      <c r="N63" t="s">
+        <v>85</v>
+      </c>
+      <c r="O63">
+        <v>4639</v>
+      </c>
+      <c r="P63">
+        <v>1336.4949340000001</v>
+      </c>
+      <c r="Q63">
+        <v>142</v>
+      </c>
+      <c r="S63">
+        <v>43.661971999999999</v>
+      </c>
+      <c r="T63">
+        <v>3.0610050000000002</v>
+      </c>
+      <c r="U63">
+        <v>199</v>
+      </c>
+      <c r="V63">
+        <v>4.2897179999999997</v>
+      </c>
+      <c r="W63">
+        <v>31.155778999999999</v>
+      </c>
+      <c r="X63">
+        <v>144</v>
+      </c>
+      <c r="Y63">
+        <v>43.055556000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" t="s">
+        <v>103</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>61</v>
+      </c>
+      <c r="G64" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64">
+        <v>1305</v>
+      </c>
+      <c r="I64">
+        <v>3.154023</v>
+      </c>
+      <c r="J64">
+        <v>81.213114750000003</v>
+      </c>
+      <c r="K64" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>4954</v>
+      </c>
+      <c r="N64" t="s">
+        <v>76</v>
+      </c>
+      <c r="O64">
+        <v>4116</v>
+      </c>
+      <c r="P64">
+        <v>1203.595724</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+      <c r="S64">
+        <v>81.213115000000002</v>
+      </c>
+      <c r="T64">
+        <v>1.482021</v>
+      </c>
+      <c r="U64">
+        <v>63</v>
+      </c>
+      <c r="V64">
+        <v>1.5306120000000001</v>
+      </c>
+      <c r="W64">
+        <v>78.634921000000006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" t="s">
+        <v>103</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s">
+        <v>30</v>
+      </c>
+      <c r="H65">
+        <v>2616</v>
+      </c>
+      <c r="I65">
+        <v>1.4082570000000001</v>
+      </c>
+      <c r="J65">
+        <v>60.292682929999998</v>
+      </c>
+      <c r="K65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>4944</v>
+      </c>
+      <c r="N65" t="s">
+        <v>114</v>
+      </c>
+      <c r="O65">
+        <v>3684</v>
+      </c>
+      <c r="P65">
+        <v>1342.019544</v>
+      </c>
+      <c r="Q65">
+        <v>82</v>
+      </c>
+      <c r="S65">
+        <v>60.292682999999997</v>
+      </c>
+      <c r="T65">
+        <v>2.225841</v>
+      </c>
+      <c r="U65">
+        <v>91</v>
+      </c>
+      <c r="V65">
+        <v>2.4701409999999999</v>
+      </c>
+      <c r="W65">
+        <v>54.32967</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>100</v>
+      </c>
+      <c r="G66" t="s">
+        <v>30</v>
+      </c>
+      <c r="H66">
+        <v>1612</v>
+      </c>
+      <c r="I66">
+        <v>1.3064519999999999</v>
+      </c>
+      <c r="J66">
+        <v>56.93</v>
+      </c>
+      <c r="K66" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>5693</v>
+      </c>
+      <c r="N66" t="s">
+        <v>112</v>
+      </c>
+      <c r="O66">
+        <v>2106</v>
+      </c>
+      <c r="P66">
+        <v>2703.2288699999999</v>
+      </c>
+      <c r="Q66">
+        <v>100</v>
+      </c>
+      <c r="S66">
+        <v>56.93</v>
+      </c>
+      <c r="T66">
+        <v>4.7483380000000004</v>
+      </c>
+      <c r="U66">
+        <v>109</v>
+      </c>
+      <c r="V66">
+        <v>5.1756890000000002</v>
+      </c>
+      <c r="W66">
+        <v>52.229357999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" t="s">
+        <v>103</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67">
+        <v>58</v>
+      </c>
+      <c r="G67" t="s">
+        <v>30</v>
+      </c>
+      <c r="H67">
+        <v>3023</v>
+      </c>
+      <c r="I67">
+        <v>1.488588</v>
+      </c>
+      <c r="J67">
+        <v>86.189655169999995</v>
+      </c>
+      <c r="K67" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>4999</v>
+      </c>
+      <c r="N67" t="s">
+        <v>110</v>
+      </c>
+      <c r="O67">
+        <v>4500</v>
+      </c>
+      <c r="P67">
+        <v>1110.8888890000001</v>
+      </c>
+      <c r="Q67">
+        <v>58</v>
+      </c>
+      <c r="S67">
+        <v>86.189655000000002</v>
+      </c>
+      <c r="T67">
+        <v>1.288889</v>
+      </c>
+      <c r="U67">
+        <v>59</v>
+      </c>
+      <c r="V67">
+        <v>1.3111109999999999</v>
+      </c>
+      <c r="W67">
+        <v>84.728814</v>
+      </c>
+      <c r="X67">
+        <v>42</v>
+      </c>
+      <c r="Y67">
+        <v>119.02381</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68">
+        <v>38</v>
+      </c>
+      <c r="G68" t="s">
+        <v>30</v>
+      </c>
+      <c r="H68">
+        <v>890</v>
+      </c>
+      <c r="I68">
+        <v>1.2393259999999999</v>
+      </c>
+      <c r="J68">
+        <v>50.631578949999998</v>
+      </c>
+      <c r="K68" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>1924</v>
+      </c>
+      <c r="N68" t="s">
+        <v>108</v>
+      </c>
+      <c r="O68">
+        <v>1103</v>
+      </c>
+      <c r="P68">
+        <v>1744.3336360000001</v>
+      </c>
+      <c r="Q68">
+        <v>38</v>
+      </c>
+      <c r="S68">
+        <v>50.631579000000002</v>
+      </c>
+      <c r="T68">
+        <v>3.4451499999999999</v>
+      </c>
+      <c r="U68">
+        <v>36</v>
+      </c>
+      <c r="V68">
+        <v>3.2638259999999999</v>
+      </c>
+      <c r="W68">
+        <v>53.444443999999997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>74</v>
+      </c>
+      <c r="D69" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69">
+        <v>62</v>
+      </c>
+      <c r="G69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H69">
+        <v>2161</v>
+      </c>
+      <c r="I69">
+        <v>1.189727</v>
+      </c>
+      <c r="J69">
+        <v>83.290322579999994</v>
+      </c>
+      <c r="K69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>5164</v>
+      </c>
+      <c r="N69" t="s">
+        <v>107</v>
+      </c>
+      <c r="O69">
+        <v>2571</v>
+      </c>
+      <c r="P69">
+        <v>2008.5569820000001</v>
+      </c>
+      <c r="Q69">
+        <v>62</v>
+      </c>
+      <c r="S69">
+        <v>83.290323000000001</v>
+      </c>
+      <c r="T69">
+        <v>2.4115129999999998</v>
+      </c>
+      <c r="U69">
+        <v>62</v>
+      </c>
+      <c r="V69">
+        <v>2.4115129999999998</v>
+      </c>
+      <c r="W69">
+        <v>83.290323000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" t="s">
+        <v>103</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>59</v>
+      </c>
+      <c r="G70" t="s">
+        <v>30</v>
+      </c>
+      <c r="H70">
+        <v>2036</v>
+      </c>
+      <c r="I70">
+        <v>1.2789779999999999</v>
+      </c>
+      <c r="J70">
+        <v>84.033898309999998</v>
+      </c>
+      <c r="K70" t="s">
+        <v>42</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>4958</v>
+      </c>
+      <c r="N70" t="s">
+        <v>105</v>
+      </c>
+      <c r="O70">
+        <v>2604</v>
+      </c>
+      <c r="P70">
+        <v>1903.9938560000001</v>
+      </c>
+      <c r="Q70">
+        <v>59</v>
+      </c>
+      <c r="S70">
+        <v>84.033897999999994</v>
+      </c>
+      <c r="T70">
+        <v>2.2657449999999999</v>
+      </c>
+      <c r="U70">
+        <v>66</v>
+      </c>
+      <c r="V70">
+        <v>2.5345620000000002</v>
+      </c>
+      <c r="W70">
+        <v>75.121212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>104</v>
+      </c>
+      <c r="D71" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71">
+        <v>117</v>
+      </c>
+      <c r="G71" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71">
+        <v>2207</v>
+      </c>
+      <c r="I71">
+        <v>1.300861</v>
+      </c>
+      <c r="J71">
+        <v>45.051282049999998</v>
+      </c>
+      <c r="K71" t="s">
+        <v>42</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>5271</v>
+      </c>
+      <c r="N71" t="s">
+        <v>101</v>
+      </c>
+      <c r="O71">
+        <v>2871</v>
+      </c>
+      <c r="P71">
+        <v>1835.9456640000001</v>
+      </c>
+      <c r="Q71">
+        <v>118</v>
+      </c>
+      <c r="S71">
+        <v>44.669491999999998</v>
+      </c>
+      <c r="T71">
+        <v>4.1100659999999998</v>
+      </c>
+      <c r="U71">
+        <v>136</v>
+      </c>
+      <c r="V71">
+        <v>4.737025</v>
+      </c>
+      <c r="W71">
+        <v>38.757353000000002</v>
+      </c>
+      <c r="X71">
+        <v>117</v>
+      </c>
+      <c r="Y71">
+        <v>45.051282</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" t="s">
+        <v>45</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
+        <v>42</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72" t="s">
+        <v>101</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>149</v>
+      </c>
+      <c r="G73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73">
+        <v>3067</v>
+      </c>
+      <c r="I73">
+        <v>1.9184870000000001</v>
+      </c>
+      <c r="J73">
+        <v>40.174496640000001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>42</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>5986</v>
+      </c>
+      <c r="N73" t="s">
+        <v>65</v>
+      </c>
+      <c r="O73">
+        <v>5884</v>
+      </c>
+      <c r="P73">
+        <v>1017.335146</v>
+      </c>
+      <c r="Q73">
+        <v>151</v>
+      </c>
+      <c r="S73">
+        <v>39.642384</v>
+      </c>
+      <c r="T73">
+        <v>2.566281</v>
+      </c>
+      <c r="U73">
+        <v>166</v>
+      </c>
+      <c r="V73">
+        <v>2.8212100000000002</v>
+      </c>
+      <c r="W73">
+        <v>36.060240999999998</v>
+      </c>
+      <c r="X73">
+        <v>149</v>
+      </c>
+      <c r="Y73">
+        <v>40.174497000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>53</v>
+      </c>
+      <c r="G74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74">
+        <v>2776</v>
+      </c>
+      <c r="I74">
+        <v>1.541066</v>
+      </c>
+      <c r="J74">
+        <v>139.83018867999999</v>
+      </c>
+      <c r="K74" t="s">
+        <v>42</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>7411</v>
+      </c>
+      <c r="N74" t="s">
+        <v>81</v>
+      </c>
+      <c r="O74">
+        <v>4278</v>
+      </c>
+      <c r="P74">
+        <v>1732.351566</v>
+      </c>
+      <c r="Q74">
+        <v>86</v>
+      </c>
+      <c r="S74">
+        <v>86.174419</v>
+      </c>
+      <c r="T74">
+        <v>2.0102850000000001</v>
+      </c>
+      <c r="U74">
+        <v>103</v>
+      </c>
+      <c r="V74">
+        <v>2.407667</v>
+      </c>
+      <c r="W74">
+        <v>71.951455999999993</v>
+      </c>
+      <c r="X74">
+        <v>53</v>
+      </c>
+      <c r="Y74">
+        <v>139.83018899999999</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>